--- a/shop_mapping.xlsx
+++ b/shop_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/keithtan_2022_accountancy_smu_edu_sg/Documents/Desktop/smu/subject/y4s2/capstone/ETL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95573B7A-4E09-4DEC-B8EE-23EFF6B31FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0094B0BF-F4C3-4388-991B-EFD5890FF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,11 +21,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>campaign_name</t>
   </si>
   <si>
+    <t>gto_name</t>
+  </si>
+  <si>
     <t>suggested_gto_name</t>
   </si>
   <si>
@@ -35,6 +38,12 @@
     <t>method</t>
   </si>
   <si>
+    <t>starbucks</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
     <t>dunkin'donuts</t>
   </si>
   <si>
@@ -44,31 +53,31 @@
     <t>fuzzy</t>
   </si>
   <si>
-    <t>starbucks</t>
-  </si>
-  <si>
-    <t>exact</t>
-  </si>
-  <si>
     <t>some cafe</t>
   </si>
   <si>
-    <t>some other cafe</t>
-  </si>
-  <si>
     <t>unmatched</t>
   </si>
   <si>
     <t>Instructions</t>
   </si>
   <si>
-    <t>DO NOT edit campaign_name or suggested_gto_name columns.</t>
-  </si>
-  <si>
-    <t>Fill confirmed_gto_name to override a suggestion or fix an unmatched entry.</t>
-  </si>
-  <si>
-    <t>Leave confirmed_gto_name blank to use the suggested match.</t>
+    <t>campaign_name: outlet name from campaign data — DO NOT edit.</t>
+  </si>
+  <si>
+    <t>gto_name: the actual GTO name used for matching (confirmed &gt; suggested).</t>
+  </si>
+  <si>
+    <t>suggested_gto_name: best automatic match — DO NOT edit.</t>
+  </si>
+  <si>
+    <t>confirmed_gto_name: fill this in to override the suggestion or fix unmatched rows.</t>
+  </si>
+  <si>
+    <t>method: how the match was found — DO NOT edit.</t>
+  </si>
+  <si>
+    <t>Unmatched rows are at the bottom — fill in confirmed_gto_name for these.</t>
   </si>
   <si>
     <t>Re-run the pipeline after editing — confirmed entries are preserved automatically.</t>
@@ -411,10 +420,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -427,37 +436,43 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -468,7 +483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -496,6 +511,21 @@
         <v>16</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shop_mapping.xlsx
+++ b/shop_mapping.xlsx
@@ -5,23 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/keithtan_2022_accountancy_smu_edu_sg/Documents/Desktop/smu/subject/y4s2/capstone/ETL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/keithtan_2022_accountancy_smu_edu_sg/Documents/Desktop/smu/subject/y4s2/capstone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0094B0BF-F4C3-4388-991B-EFD5890FF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_2843CF6777360EDB62996FD940E76823C5066009" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{413621C8-59AE-4C07-B173-EBB5447276F3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
     <sheet name="instructions" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$E$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
   <si>
     <t>campaign_name</t>
   </si>
@@ -38,46 +41,277 @@
     <t>method</t>
   </si>
   <si>
-    <t>starbucks</t>
+    <t>zoff</t>
   </si>
   <si>
     <t>exact</t>
   </si>
   <si>
-    <t>dunkin'donuts</t>
+    <t>fila</t>
+  </si>
+  <si>
+    <t>lac</t>
+  </si>
+  <si>
+    <t>watsons</t>
+  </si>
+  <si>
+    <t>guardian b4</t>
+  </si>
+  <si>
+    <t>guardian</t>
+  </si>
+  <si>
+    <t>fuzzy</t>
+  </si>
+  <si>
+    <t>eu yan sang</t>
+  </si>
+  <si>
+    <t>royce'</t>
+  </si>
+  <si>
+    <t>adidas</t>
+  </si>
+  <si>
+    <t>jeric salon</t>
+  </si>
+  <si>
+    <t>samsonite</t>
+  </si>
+  <si>
+    <t>nb 1906</t>
+  </si>
+  <si>
+    <t>muji</t>
+  </si>
+  <si>
+    <t>muji 无印良品</t>
+  </si>
+  <si>
+    <t>the 1872 clipper tea co.</t>
+  </si>
+  <si>
+    <t>hoka</t>
+  </si>
+  <si>
+    <t>awfully chocolate</t>
+  </si>
+  <si>
+    <t>rive gauche patisserie</t>
+  </si>
+  <si>
+    <t>lavender</t>
+  </si>
+  <si>
+    <t>daiso</t>
+  </si>
+  <si>
+    <t>daiso japan</t>
+  </si>
+  <si>
+    <t>letao / tokyo milk cheese factory</t>
+  </si>
+  <si>
+    <t>nostalgic modern letao northern sweets manner / tokyo milk cheese factory</t>
+  </si>
+  <si>
+    <t>mos japanese fine foods</t>
+  </si>
+  <si>
+    <t>cinnabon</t>
+  </si>
+  <si>
+    <t>kee wah bakery</t>
+  </si>
+  <si>
+    <t>chateraise</t>
+  </si>
+  <si>
+    <t>tempura tendon tenya</t>
+  </si>
+  <si>
+    <t>hang heung hong kong</t>
+  </si>
+  <si>
+    <t>香港 恆香 始創於一九二零 hang heung hong kong since 1920</t>
+  </si>
+  <si>
+    <t>dunkin' donuts</t>
   </si>
   <si>
     <t>dunkin'</t>
   </si>
   <si>
-    <t>fuzzy</t>
-  </si>
-  <si>
-    <t>some cafe</t>
+    <t>monster curry</t>
+  </si>
+  <si>
+    <t>each a cup</t>
+  </si>
+  <si>
+    <t>guzman y gomez mexican kitchen</t>
+  </si>
+  <si>
+    <t>lee wee &amp; brothers</t>
+  </si>
+  <si>
+    <t>marutama ramen</t>
+  </si>
+  <si>
+    <t>marutama ra-men</t>
+  </si>
+  <si>
+    <t>hublot</t>
   </si>
   <si>
     <t>unmatched</t>
   </si>
   <si>
+    <t>twg tea</t>
+  </si>
+  <si>
+    <t>graff</t>
+  </si>
+  <si>
+    <t>franck muller</t>
+  </si>
+  <si>
+    <t>loro piana</t>
+  </si>
+  <si>
+    <t>jd sports</t>
+  </si>
+  <si>
+    <t>harry winston</t>
+  </si>
+  <si>
+    <t>jasons deli</t>
+  </si>
+  <si>
+    <t>a. lange &amp; sohne</t>
+  </si>
+  <si>
+    <t>vacheron constantin</t>
+  </si>
+  <si>
+    <t>108 matcha saro</t>
+  </si>
+  <si>
+    <t>gto_only</t>
+  </si>
+  <si>
+    <t>180o popcorn</t>
+  </si>
+  <si>
+    <t>2xu</t>
+  </si>
+  <si>
+    <t>bao bao 宝包</t>
+  </si>
+  <si>
+    <t>bengawan solo</t>
+  </si>
+  <si>
+    <t>boost&amp;</t>
+  </si>
+  <si>
+    <t>breadtalk</t>
+  </si>
+  <si>
+    <t>donq éditer / mini one</t>
+  </si>
+  <si>
+    <t>food opera / toast box</t>
+  </si>
+  <si>
+    <t>har har chicken</t>
+  </si>
+  <si>
+    <t>heytea 喜茶</t>
+  </si>
+  <si>
+    <t>jasons deli by cold storage</t>
+  </si>
+  <si>
+    <t>jd, king of trainers</t>
+  </si>
+  <si>
+    <t>koi thé</t>
+  </si>
+  <si>
+    <t>lim chee guan</t>
+  </si>
+  <si>
+    <t>old chang kee</t>
+  </si>
+  <si>
+    <t>pezzo</t>
+  </si>
+  <si>
+    <t>pocha! korean street dining</t>
+  </si>
+  <si>
+    <t>puma</t>
+  </si>
+  <si>
+    <t>ramen nagi</t>
+  </si>
+  <si>
+    <t>rookie kids</t>
+  </si>
+  <si>
+    <t>sally's by neo group</t>
+  </si>
+  <si>
+    <t>shihlin taiwan street snacks</t>
+  </si>
+  <si>
+    <t>smile martabak</t>
+  </si>
+  <si>
+    <t>super sushi</t>
+  </si>
+  <si>
+    <t>teppei syokudo</t>
+  </si>
+  <si>
+    <t>the north face</t>
+  </si>
+  <si>
+    <t>the soup spoon</t>
+  </si>
+  <si>
+    <t>tori q</t>
+  </si>
+  <si>
+    <t>twyst</t>
+  </si>
+  <si>
+    <t>ya kun kaya toast</t>
+  </si>
+  <si>
+    <t>街边小贩 hawkers' street</t>
+  </si>
+  <si>
     <t>Instructions</t>
   </si>
   <si>
     <t>campaign_name: outlet name from campaign data — DO NOT edit.</t>
   </si>
   <si>
-    <t>gto_name: the actual GTO name used for matching (confirmed &gt; suggested).</t>
+    <t>gto_name: the GTO name used for matching (confirmed &gt; suggested).</t>
   </si>
   <si>
     <t>suggested_gto_name: best automatic match — DO NOT edit.</t>
   </si>
   <si>
-    <t>confirmed_gto_name: fill this in to override the suggestion or fix unmatched rows.</t>
-  </si>
-  <si>
-    <t>method: how the match was found — DO NOT edit.</t>
-  </si>
-  <si>
-    <t>Unmatched rows are at the bottom — fill in confirmed_gto_name for these.</t>
+    <t>confirmed_gto_name: fill this in to override a suggestion or fix unmatched rows.</t>
+  </si>
+  <si>
+    <t>method: exact/fuzzy/confirmed = campaign matched to GTO; unmatched = campaign with no GTO match; gto_only = GTO shop with no campaign activity.</t>
+  </si>
+  <si>
+    <t>Unmatched campaign rows and gto_only rows are at the bottom.</t>
   </si>
   <si>
     <t>Re-run the pipeline after editing — confirmed entries are preserved automatically.</t>
@@ -87,7 +321,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,16 +329,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -112,12 +358,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,23 +685,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -459,24 +729,763 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B26" t="s">
         <v>11</v>
       </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>83</v>
+      </c>
+      <c r="E59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>86</v>
+      </c>
+      <c r="E62" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E64" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>49</v>
+      </c>
+      <c r="E68" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E72" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>55</v>
+      </c>
+      <c r="E74" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E74">
+      <sortCondition ref="E1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -487,43 +1496,43 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>12</v>
+      <c r="A1" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
